--- a/swe402_course_schedule.xlsx
+++ b/swe402_course_schedule.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/omarhammad/Documents/code_local/gaming_course/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/omarhammad/Documents/code_local/swe402/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65EB164-7090-8144-94E3-18F36A92A093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B36742-602F-7741-8FE2-46965B5BBA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="920" windowWidth="34240" windowHeight="20120" xr2:uid="{71EA9F77-12E9-CF40-801C-D2627967425B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Calendar_v3" sheetId="7" r:id="rId1"/>
-    <sheet name="Old_Calendar_links" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId3"/>
+    <sheet name="Calendar_v4" sheetId="8" r:id="rId1"/>
+    <sheet name="Calendar_v3" sheetId="7" r:id="rId2"/>
+    <sheet name="Old_Calendar_links" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="129">
   <si>
     <t>Week</t>
   </si>
@@ -441,6 +442,18 @@
   </si>
   <si>
     <t>Programming Best Prcts &amp; Documentation</t>
+  </si>
+  <si>
+    <t>Adv Graphics + Final Pres</t>
+  </si>
+  <si>
+    <t>Project time</t>
+  </si>
+  <si>
+    <t>Progress update</t>
+  </si>
+  <si>
+    <t>VR/AR (Optional)</t>
   </si>
 </sst>
 </file>
@@ -530,7 +543,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -582,6 +595,49 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -603,49 +659,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -980,22 +994,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30402BE8-464E-1844-A0F5-8774673BC6B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60723551-0FAE-D144-9066-3CA80214ED68}">
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="37.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" style="40"/>
+    <col min="7" max="7" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="29" t="s">
         <v>77</v>
       </c>
       <c r="C1" s="8" t="s">
@@ -1010,18 +1024,18 @@
       <c r="F1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="30" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="26">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="32" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
@@ -1030,73 +1044,73 @@
       <c r="D2" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="19">
         <v>1</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="31" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="26">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="34"/>
+      <c r="B3" s="33"/>
       <c r="C3" t="s">
         <v>103</v>
       </c>
       <c r="D3" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="19">
         <v>2</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="31" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="26">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="34"/>
+      <c r="B4" s="33"/>
       <c r="C4" t="s">
         <v>124</v>
       </c>
       <c r="D4" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="19">
         <v>3</v>
       </c>
       <c r="G4" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="40">
+      <c r="H4" s="31">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="26">
+      <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="36" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="27"/>
       <c r="F5" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="32" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
@@ -1105,73 +1119,70 @@
       <c r="D6" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="19">
         <v>4</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="31" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="26">
+      <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" t="s">
         <v>95</v>
       </c>
       <c r="D7" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="19">
         <v>5</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="31" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" t="s">
         <v>94</v>
       </c>
       <c r="D8" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="19">
         <v>6</v>
       </c>
-      <c r="G8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H8" s="40" t="s">
+      <c r="H8" s="31" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="26">
+      <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="36" t="s">
+      <c r="B9" s="33"/>
+      <c r="C9" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="36"/>
+      <c r="E9" s="27"/>
       <c r="F9" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="32" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
@@ -1180,126 +1191,129 @@
       <c r="D10" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="19">
         <v>7</v>
       </c>
-      <c r="H10" s="40" t="s">
+      <c r="H10" s="31" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="26">
+      <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="33"/>
       <c r="C11" t="s">
         <v>97</v>
       </c>
       <c r="D11" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="19">
         <v>8</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="31" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="26">
+      <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="33"/>
       <c r="C12" t="s">
         <v>91</v>
       </c>
       <c r="D12" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="19">
         <v>9</v>
       </c>
-      <c r="G12" t="s">
-        <v>107</v>
-      </c>
-      <c r="H12" s="40">
+      <c r="H12" s="31">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="26">
+      <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="36" t="s">
+      <c r="B13" s="33"/>
+      <c r="C13" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="36"/>
-      <c r="F13" t="s">
+      <c r="E13" s="27"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="19">
+        <v>13</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
-        <v>13</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="E14" s="19">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="19">
+        <v>14</v>
+      </c>
+      <c r="B15" s="33"/>
+      <c r="C15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="D14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="26">
-        <v>10</v>
-      </c>
-      <c r="H14" s="40" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="26">
-        <v>14</v>
-      </c>
-      <c r="B15" s="34"/>
-      <c r="C15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="26">
+      <c r="E15" s="19">
         <v>11</v>
       </c>
-      <c r="H15" s="40">
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" s="31">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="26">
+      <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="34"/>
+      <c r="B16" s="33"/>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="26">
+        <v>128</v>
+      </c>
+      <c r="E16" s="19">
         <v>12</v>
       </c>
-      <c r="G16" t="s">
-        <v>108</v>
+      <c r="G16" s="41" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="26"/>
+      <c r="A17" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1313,6 +1327,339 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30402BE8-464E-1844-A0F5-8774673BC6B9}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="19">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="19">
+        <v>1</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="19">
+        <v>2</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="19">
+        <v>3</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="19">
+        <v>4</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="19">
+        <v>5</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="19">
+        <v>4</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="19">
+        <v>6</v>
+      </c>
+      <c r="B7" s="33"/>
+      <c r="C7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="19">
+        <v>5</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="19">
+        <v>7</v>
+      </c>
+      <c r="B8" s="33"/>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="19">
+        <v>6</v>
+      </c>
+      <c r="G8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="19">
+        <v>8</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="27"/>
+      <c r="F9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="19">
+        <v>9</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="19">
+        <v>7</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="19">
+        <v>10</v>
+      </c>
+      <c r="B11" s="33"/>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="19">
+        <v>8</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="19">
+        <v>11</v>
+      </c>
+      <c r="B12" s="33"/>
+      <c r="C12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="19">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="31">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="19">
+        <v>12</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="27"/>
+      <c r="F13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="19">
+        <v>13</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="19">
+        <v>10</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="19">
+        <v>14</v>
+      </c>
+      <c r="B15" s="33"/>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="19">
+        <v>11</v>
+      </c>
+      <c r="H15" s="31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="19">
+        <v>15</v>
+      </c>
+      <c r="B16" s="33"/>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="19">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3747D164-E7E5-CD44-952E-1DB729307968}">
   <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1324,7 +1671,7 @@
     <col min="5" max="5" width="92.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="43" style="1" customWidth="1"/>
     <col min="7" max="7" width="49" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.33203125" style="27" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" style="20" customWidth="1"/>
     <col min="9" max="9" width="20.5" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.6640625" style="1" customWidth="1"/>
     <col min="11" max="16384" width="10.83203125" style="1"/>
@@ -1352,7 +1699,7 @@
       <c r="G1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="20" t="s">
         <v>56</v>
       </c>
       <c r="I1" s="10" t="s">
@@ -1375,7 +1722,7 @@
       <c r="C2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="19" t="s">
         <v>57</v>
       </c>
       <c r="E2" s="14" t="s">
@@ -1387,7 +1734,7 @@
       <c r="G2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="24" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1401,7 +1748,7 @@
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="19" t="s">
         <v>57</v>
       </c>
       <c r="E3" s="15" t="s">
@@ -1413,7 +1760,7 @@
       <c r="G3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="26" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1436,7 +1783,7 @@
       <c r="G4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="24" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1447,13 +1794,13 @@
       <c r="B5" s="3">
         <v>46054</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="35" t="s">
         <v>49</v>
       </c>
       <c r="F5" s="18" t="s">
@@ -1462,7 +1809,7 @@
       <c r="G5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="28"/>
+      <c r="H5" s="21"/>
       <c r="I5" s="12" t="s">
         <v>18</v>
       </c>
@@ -1474,9 +1821,9 @@
       <c r="B6" s="3">
         <v>46061</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="20"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="35"/>
       <c r="F6" s="1" t="s">
         <v>30</v>
       </c>
@@ -1492,13 +1839,13 @@
       <c r="B7" s="3">
         <v>46068</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="21"/>
+      <c r="E7" s="36"/>
       <c r="F7" t="s">
         <v>29</v>
       </c>
@@ -1507,23 +1854,23 @@
       </c>
       <c r="H7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3">
         <v>46075</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="21"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="36"/>
       <c r="F8" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="29"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
@@ -1532,13 +1879,13 @@
       <c r="B9" s="3">
         <v>46082</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="37" t="s">
         <v>50</v>
       </c>
       <c r="F9" s="18" t="s">
@@ -1547,7 +1894,7 @@
       <c r="G9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="21"/>
       <c r="I9" s="12" t="s">
         <v>28</v>
       </c>
@@ -1559,9 +1906,9 @@
       <c r="B10" s="3">
         <v>46089</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="22"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="37"/>
       <c r="F10" s="1" t="s">
         <v>32</v>
       </c>
@@ -1581,7 +1928,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="30"/>
+      <c r="H11" s="23"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1598,7 +1945,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="30"/>
+      <c r="H12" s="23"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1610,13 +1957,13 @@
       <c r="B13" s="3">
         <v>46110</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="34" t="s">
         <v>51</v>
       </c>
       <c r="F13" t="s">
@@ -1634,9 +1981,9 @@
       <c r="B14" s="3">
         <v>46117</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="19"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="1" t="s">
         <v>36</v>
       </c>
@@ -1666,7 +2013,7 @@
       <c r="G15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="28"/>
+      <c r="H15" s="21"/>
       <c r="I15" s="12" t="s">
         <v>44</v>
       </c>
@@ -1704,7 +2051,7 @@
       <c r="C17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="19" t="s">
         <v>57</v>
       </c>
       <c r="E17" s="15" t="s">
@@ -1738,7 +2085,7 @@
       <c r="G18" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="28"/>
+      <c r="H18" s="21"/>
       <c r="I18" s="12" t="s">
         <v>45</v>
       </c>
@@ -1763,7 +2110,7 @@
       <c r="G19" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="25"/>
       <c r="I19" s="16" t="s">
         <v>5</v>
       </c>
@@ -1798,7 +2145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD4EECD-0CCA-EE4A-A436-C1C220BC99F4}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
